--- a/excel-files/MALABON/CATMON IS.xlsx
+++ b/excel-files/MALABON/CATMON IS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA51F082-A9A6-4C8D-9645-38F11A94B173}"/>
+  <xr:revisionPtr revIDLastSave="323" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F08E07E-365D-4257-96AD-314CD84D2918}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -67,6 +67,9 @@
     <t>Reading and Literacy</t>
   </si>
   <si>
+    <t>RO</t>
+  </si>
+  <si>
     <t>Language</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
   </si>
   <si>
     <t>Math</t>
+  </si>
+  <si>
+    <t>CO</t>
   </si>
   <si>
     <t>Science</t>
@@ -221,9 +227,6 @@
   </si>
   <si>
     <t>KINDER</t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>MAPEH</t>
@@ -425,7 +428,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -495,6 +498,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -628,7 +643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -743,6 +758,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3514,13 +3544,15 @@
       <c r="C2" s="1">
         <v>478</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="43">
         <v>621</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="43">
         <v>2024</v>
       </c>
-      <c r="F2" s="5"/>
+      <c r="F2" s="44" t="s">
+        <v>9</v>
+      </c>
       <c r="G2" s="3">
         <f>IF((C2-D2)&lt;0,0,C2-D2)</f>
         <v>0</v>
@@ -3535,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>478</v>
@@ -3557,18 +3589,20 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>478</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="43">
         <v>621</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="43">
         <v>2024</v>
       </c>
-      <c r="F4" s="5"/>
+      <c r="F4" s="44" t="s">
+        <v>9</v>
+      </c>
       <c r="G4" s="3">
         <f>IF((C4-D4)&lt;0,0,C4-D4)</f>
         <v>0</v>
@@ -3583,18 +3617,20 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>478</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="43">
         <v>621</v>
       </c>
-      <c r="E5" s="1">
-        <v>2024</v>
-      </c>
-      <c r="F5" s="5"/>
+      <c r="E5" s="43">
+        <v>2025</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>9</v>
+      </c>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G6" si="0">IF((C5-D5)&lt;0,0,C5-D5)</f>
         <v>0</v>
@@ -3609,7 +3645,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1">
         <v>478</v>
@@ -3658,7 +3694,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1">
         <v>516</v>
@@ -3680,7 +3716,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1">
         <v>516</v>
@@ -3702,21 +3738,27 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>516</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="D11" s="43">
+        <v>536</v>
+      </c>
+      <c r="E11" s="42">
+        <v>2025</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.5">
@@ -3724,7 +3766,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1">
         <v>516</v>
@@ -3773,7 +3815,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1">
         <v>547</v>
@@ -3795,7 +3837,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1">
         <v>547</v>
@@ -3817,7 +3859,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1">
         <v>547</v>
@@ -3839,7 +3881,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1">
         <v>547</v>
@@ -3861,7 +3903,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" s="1">
         <v>547</v>
@@ -3893,7 +3935,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1">
         <v>489</v>
@@ -3919,18 +3961,20 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1">
         <v>489</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="43">
         <v>548</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="43">
         <v>2024</v>
       </c>
-      <c r="F22" s="5"/>
+      <c r="F22" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3945,18 +3989,20 @@
         <v>4</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23" s="1">
         <v>489</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="43">
         <v>548</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="43">
         <v>2025</v>
       </c>
-      <c r="F23" s="5"/>
+      <c r="F23" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3971,18 +4017,20 @@
         <v>4</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1">
         <v>489</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="43">
         <v>548</v>
       </c>
-      <c r="E24" s="1">
-        <v>2025</v>
-      </c>
-      <c r="F24" s="5"/>
+      <c r="E24" s="43">
+        <v>2024</v>
+      </c>
+      <c r="F24" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3997,7 +4045,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C25" s="1">
         <v>489</v>
@@ -4023,7 +4071,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>489</v>
@@ -4049,7 +4097,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C27" s="1">
         <v>489</v>
@@ -4075,7 +4123,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C28" s="1">
         <v>489</v>
@@ -4097,21 +4145,27 @@
         <v>4</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C29" s="1">
         <v>489</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="D29" s="43">
+        <v>548</v>
+      </c>
+      <c r="E29" s="42">
+        <v>2025</v>
+      </c>
+      <c r="F29" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G29" s="3">
-        <f t="shared" si="4"/>
-        <v>489</v>
+        <f>IF((C29-D29)&lt;0,0,C29-D29)</f>
+        <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4129,7 +4183,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1">
         <v>449</v>
@@ -4155,7 +4209,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1">
         <v>449</v>
@@ -4177,7 +4231,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1">
         <v>449</v>
@@ -4199,7 +4253,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1">
         <v>449</v>
@@ -4221,7 +4275,7 @@
         <v>5</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C35" s="1">
         <v>449</v>
@@ -4247,18 +4301,20 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1">
         <v>449</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="43">
         <v>595</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="43">
         <v>2025</v>
       </c>
-      <c r="F36" s="5"/>
+      <c r="F36" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4273,18 +4329,20 @@
         <v>5</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C37" s="1">
         <v>449</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="43">
         <v>595</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="43">
         <v>2025</v>
       </c>
-      <c r="F37" s="5"/>
+      <c r="F37" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4299,21 +4357,27 @@
         <v>5</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C38" s="1">
         <v>449</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="D38" s="43">
+        <v>595</v>
+      </c>
+      <c r="E38" s="42">
+        <v>2025</v>
+      </c>
+      <c r="F38" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
-        <v>449</v>
+        <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4321,7 +4385,7 @@
         <v>5</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C39" s="1">
         <v>449</v>
@@ -4353,7 +4417,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1">
         <v>462</v>
@@ -4375,7 +4439,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1">
         <v>462</v>
@@ -4397,7 +4461,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C43" s="1">
         <v>462</v>
@@ -4419,7 +4483,7 @@
         <v>6</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C44" s="1">
         <v>462</v>
@@ -4441,7 +4505,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C45" s="1">
         <v>462</v>
@@ -4463,7 +4527,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1">
         <v>462</v>
@@ -4485,7 +4549,7 @@
         <v>6</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C47" s="1">
         <v>462</v>
@@ -4507,7 +4571,7 @@
         <v>6</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C48" s="1">
         <v>462</v>
@@ -4529,7 +4593,7 @@
         <v>6</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C49" s="1">
         <v>462</v>
@@ -4561,7 +4625,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C51" s="10">
         <v>500</v>
@@ -4587,7 +4651,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C52" s="10">
         <v>500</v>
@@ -4609,7 +4673,7 @@
         <v>7</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C53" s="10">
         <v>500</v>
@@ -4635,17 +4699,23 @@
         <v>7</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C54" s="10">
         <v>500</v>
       </c>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="12"/>
+      <c r="D54" s="43">
+        <v>484</v>
+      </c>
+      <c r="E54" s="42">
+        <v>2025</v>
+      </c>
+      <c r="F54" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G54" s="3">
         <f t="shared" si="10"/>
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="H54" s="4">
         <f t="shared" si="11"/>
@@ -4657,7 +4727,7 @@
         <v>7</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C55" s="10">
         <v>500</v>
@@ -4679,7 +4749,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C56" s="10">
         <v>500</v>
@@ -4705,18 +4775,20 @@
         <v>7</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C57" s="10">
         <v>500</v>
       </c>
-      <c r="D57" s="10">
+      <c r="D57" s="43">
         <v>484</v>
       </c>
-      <c r="E57" s="10">
+      <c r="E57" s="43">
         <v>2025</v>
       </c>
-      <c r="F57" s="12"/>
+      <c r="F57" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G57" s="3">
         <f t="shared" si="10"/>
         <v>16</v>
@@ -4731,18 +4803,20 @@
         <v>7</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C58" s="10">
         <v>500</v>
       </c>
-      <c r="D58" s="10">
+      <c r="D58" s="43">
         <v>484</v>
       </c>
-      <c r="E58" s="10">
+      <c r="E58" s="43">
         <v>2025</v>
       </c>
-      <c r="F58" s="12"/>
+      <c r="F58" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G58" s="3">
         <f t="shared" si="10"/>
         <v>16</v>
@@ -4757,18 +4831,20 @@
         <v>7</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C59" s="10">
         <v>500</v>
       </c>
-      <c r="D59" s="10">
+      <c r="D59" s="43">
         <v>484</v>
       </c>
-      <c r="E59" s="10">
+      <c r="E59" s="43">
         <v>2025</v>
       </c>
-      <c r="F59" s="12"/>
+      <c r="F59" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G59" s="3">
         <f t="shared" si="10"/>
         <v>16</v>
@@ -4793,7 +4869,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C61" s="10">
         <v>447</v>
@@ -4815,7 +4891,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C62" s="10">
         <v>447</v>
@@ -4837,18 +4913,20 @@
         <v>8</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C63" s="10">
         <v>447</v>
       </c>
-      <c r="D63" s="10">
+      <c r="D63" s="43">
         <v>420</v>
       </c>
-      <c r="E63" s="10">
+      <c r="E63" s="43">
         <v>2025</v>
       </c>
-      <c r="F63" s="12"/>
+      <c r="F63" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G63" s="3">
         <f t="shared" si="12"/>
         <v>27</v>
@@ -4863,18 +4941,20 @@
         <v>8</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C64" s="10">
         <v>447</v>
       </c>
-      <c r="D64" s="10">
+      <c r="D64" s="43">
         <v>420</v>
       </c>
-      <c r="E64" s="10">
+      <c r="E64" s="43">
         <v>2025</v>
       </c>
-      <c r="F64" s="12"/>
+      <c r="F64" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="G64" s="3">
         <f t="shared" si="12"/>
         <v>27</v>
@@ -4889,7 +4969,7 @@
         <v>8</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C65" s="10">
         <v>447</v>
@@ -4915,7 +4995,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C66" s="10">
         <v>447</v>
@@ -4937,7 +5017,7 @@
         <v>8</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C67" s="10">
         <v>447</v>
@@ -4959,7 +5039,7 @@
         <v>8</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C68" s="10">
         <v>447</v>
@@ -4981,7 +5061,7 @@
         <v>8</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C69" s="10">
         <v>447</v>
@@ -5013,7 +5093,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C71" s="10">
         <v>437</v>
@@ -5035,7 +5115,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C72" s="10">
         <v>437</v>
@@ -5057,7 +5137,7 @@
         <v>9</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C73" s="10">
         <v>437</v>
@@ -5079,7 +5159,7 @@
         <v>9</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C74" s="10">
         <v>437</v>
@@ -5101,7 +5181,7 @@
         <v>9</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C75" s="10">
         <v>437</v>
@@ -5123,7 +5203,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C76" s="10">
         <v>437</v>
@@ -5145,7 +5225,7 @@
         <v>9</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C77" s="10">
         <v>437</v>
@@ -5167,7 +5247,7 @@
         <v>9</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C78" s="10">
         <v>437</v>
@@ -5189,7 +5269,7 @@
         <v>9</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C79" s="10">
         <v>437</v>
@@ -5221,7 +5301,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C81" s="10">
         <v>347</v>
@@ -5243,7 +5323,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C82" s="10">
         <v>347</v>
@@ -5265,7 +5345,7 @@
         <v>10</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C83" s="10">
         <v>347</v>
@@ -5287,7 +5367,7 @@
         <v>10</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C84" s="10">
         <v>347</v>
@@ -5309,7 +5389,7 @@
         <v>10</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C85" s="10">
         <v>347</v>
@@ -5331,7 +5411,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C86" s="10">
         <v>347</v>
@@ -5353,7 +5433,7 @@
         <v>10</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C87" s="10">
         <v>347</v>
@@ -5375,7 +5455,7 @@
         <v>10</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C88" s="10">
         <v>347</v>
@@ -5397,7 +5477,7 @@
         <v>10</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C89" s="10">
         <v>347</v>
@@ -5426,10 +5506,10 @@
     </row>
     <row r="91" spans="1:8" ht="39.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -5446,10 +5526,10 @@
     </row>
     <row r="92" spans="1:8" ht="27.75" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -5466,10 +5546,10 @@
     </row>
     <row r="93" spans="1:8" ht="27.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
@@ -5486,10 +5566,10 @@
     </row>
     <row r="94" spans="1:8" ht="27.75" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
@@ -5506,10 +5586,10 @@
     </row>
     <row r="95" spans="1:8" ht="40.5" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
@@ -5526,10 +5606,10 @@
     </row>
     <row r="96" spans="1:8" ht="38.25" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
@@ -5546,10 +5626,10 @@
     </row>
     <row r="97" spans="1:8" ht="27.75" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -5566,10 +5646,10 @@
     </row>
     <row r="98" spans="1:8" ht="47.25" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -5591,10 +5671,10 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E2:E6 E51:E59 E31:E39 E41:E49 E91:E98 E71:E79 E81:E89 E8:E12 E61:E69" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E61:E69 E2:E6 E51:E59 E31:E39 E41:E49 E91:E98 E71:E79 E81:E89 E8:E12 E21:E29" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F21:F29" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5607,7 +5687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5637,38 +5717,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="D1" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5681,81 +5761,81 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N2" s="40" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="41" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z2" s="41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AA2" s="26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="32">
@@ -5765,14 +5845,14 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3840</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="45">
         <v>646</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="46">
         <v>2025</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>61</v>
+      <c r="G3" s="44" t="s">
+        <v>14</v>
       </c>
       <c r="H3" s="34">
         <f>IF((D3-E3)&lt;0,0,(D3-E3))</f>
@@ -5793,7 +5873,7 @@
         <v>2025</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="N3" s="5">
         <f t="shared" ref="N3" si="0">IF((J3-K3)&lt;0,0,(J3-K3))</f>
@@ -5814,7 +5894,7 @@
         <v>2025</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="T3" s="34">
         <f>IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
@@ -5835,7 +5915,7 @@
         <v>2025</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="Z3" s="34">
         <f>IF((V3-W3)&lt;0,0,(V3-W3))</f>
@@ -5875,7 +5955,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="1"/>
       <c r="G5" s="5" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="H5" s="5">
         <f t="shared" ref="H5:H77" si="2">IF((D5-E5)&lt;0,0,(D5-E5))</f>
@@ -5890,7 +5970,9 @@
         <v>3824</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="1"/>
+      <c r="L5" s="1">
+        <v>2024</v>
+      </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
         <f t="shared" ref="N5" si="4">IF((J5-K5)&lt;0,0,(J5-K5))</f>
@@ -5936,7 +6018,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>478</v>
@@ -6007,7 +6089,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1">
         <v>478</v>
@@ -6078,7 +6160,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>478</v>
@@ -6149,7 +6231,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1">
         <v>478</v>
@@ -6220,7 +6302,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1">
         <v>478</v>
@@ -6291,7 +6373,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1">
         <v>478</v>
@@ -6362,7 +6444,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="1">
         <v>478</v>
@@ -6517,7 +6599,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1">
         <v>516</v>
@@ -6588,7 +6670,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1">
         <v>516</v>
@@ -6659,7 +6741,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="1">
         <v>516</v>
@@ -6732,7 +6814,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>516</v>
@@ -6805,7 +6887,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1">
         <v>516</v>
@@ -6878,7 +6960,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1">
         <v>516</v>
@@ -6951,7 +7033,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1">
         <v>516</v>
@@ -7107,7 +7189,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1">
         <v>547</v>
@@ -7178,7 +7260,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1">
         <v>547</v>
@@ -7249,7 +7331,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>547</v>
@@ -7320,7 +7402,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27" s="1">
         <v>547</v>
@@ -7391,7 +7473,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1">
         <v>547</v>
@@ -7462,7 +7544,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1">
         <v>547</v>
@@ -7533,7 +7615,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1">
         <v>547</v>
@@ -7604,7 +7686,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1">
         <v>547</v>
@@ -7689,7 +7771,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1">
         <v>489</v>
@@ -7760,7 +7842,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1">
         <v>489</v>
@@ -7831,7 +7913,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1">
         <v>489</v>
@@ -7902,7 +7984,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1">
         <v>489</v>
@@ -7973,7 +8055,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C37" s="1">
         <v>489</v>
@@ -8044,7 +8126,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1">
         <v>489</v>
@@ -8115,7 +8197,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C39" s="1">
         <v>489</v>
@@ -8186,7 +8268,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C40" s="1">
         <v>489</v>
@@ -8257,7 +8339,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C41" s="1">
         <v>489</v>
@@ -8342,7 +8424,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1">
         <v>449</v>
@@ -8415,7 +8497,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1">
         <v>449</v>
@@ -8486,7 +8568,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1">
         <v>449</v>
@@ -8559,7 +8641,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1">
         <v>449</v>
@@ -8630,7 +8712,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1">
         <v>449</v>
@@ -8701,7 +8783,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1">
         <v>449</v>
@@ -8772,7 +8854,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C49" s="1">
         <v>449</v>
@@ -8843,7 +8925,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C50" s="1">
         <v>449</v>
@@ -8914,7 +8996,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C51" s="1">
         <v>449</v>
@@ -8999,7 +9081,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1">
         <v>462</v>
@@ -9072,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1">
         <v>462</v>
@@ -9145,7 +9227,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" s="1">
         <v>462</v>
@@ -9218,7 +9300,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="1">
         <v>462</v>
@@ -9291,7 +9373,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C57" s="1">
         <v>462</v>
@@ -9364,7 +9446,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1">
         <v>462</v>
@@ -9437,7 +9519,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C59" s="1">
         <v>462</v>
@@ -9510,7 +9592,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C60" s="1">
         <v>462</v>
@@ -9581,7 +9663,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C61" s="1">
         <v>462</v>
@@ -9668,7 +9750,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C63" s="10">
         <v>500</v>
@@ -9739,7 +9821,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C64" s="10">
         <v>500</v>
@@ -9810,7 +9892,7 @@
         <v>7</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C65" s="10">
         <v>500</v>
@@ -9881,7 +9963,7 @@
         <v>7</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C66" s="10">
         <v>500</v>
@@ -9952,7 +10034,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C67" s="10">
         <v>500</v>
@@ -10023,7 +10105,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C68" s="10">
         <v>500</v>
@@ -10094,7 +10176,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C69" s="10">
         <v>500</v>
@@ -10165,7 +10247,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C70" s="10">
         <v>500</v>
@@ -10236,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C71" s="10">
         <v>500</v>
@@ -10321,7 +10403,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C73" s="10">
         <v>447</v>
@@ -10392,7 +10474,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C74" s="10">
         <v>447</v>
@@ -10463,7 +10545,7 @@
         <v>8</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C75" s="10">
         <v>447</v>
@@ -10534,7 +10616,7 @@
         <v>8</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C76" s="10">
         <v>447</v>
@@ -10605,7 +10687,7 @@
         <v>8</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C77" s="10">
         <v>447</v>
@@ -10676,7 +10758,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C78" s="10">
         <v>447</v>
@@ -10747,7 +10829,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C79" s="10">
         <v>447</v>
@@ -10818,7 +10900,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C80" s="10">
         <v>447</v>
@@ -10889,7 +10971,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C81" s="10">
         <v>447</v>
@@ -10974,7 +11056,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C83" s="10">
         <v>437</v>
@@ -11045,7 +11127,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C84" s="10">
         <v>437</v>
@@ -11116,7 +11198,7 @@
         <v>9</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C85" s="10">
         <v>437</v>
@@ -11187,7 +11269,7 @@
         <v>9</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C86" s="10">
         <v>437</v>
@@ -11258,7 +11340,7 @@
         <v>9</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C87" s="10">
         <v>437</v>
@@ -11329,7 +11411,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C88" s="10">
         <v>437</v>
@@ -11400,7 +11482,7 @@
         <v>9</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C89" s="10">
         <v>437</v>
@@ -11471,7 +11553,7 @@
         <v>9</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C90" s="10">
         <v>437</v>
@@ -11542,7 +11624,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C91" s="10">
         <v>437</v>
@@ -11627,7 +11709,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C93" s="10">
         <v>347</v>
@@ -11698,7 +11780,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C94" s="10">
         <v>347</v>
@@ -11769,7 +11851,7 @@
         <v>10</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C95" s="10">
         <v>347</v>
@@ -11840,7 +11922,7 @@
         <v>10</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C96" s="10">
         <v>347</v>
@@ -11911,7 +11993,7 @@
         <v>10</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C97" s="10">
         <v>347</v>
@@ -11982,7 +12064,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C98" s="10">
         <v>347</v>
@@ -12053,7 +12135,7 @@
         <v>10</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C99" s="10">
         <v>347</v>
@@ -12124,7 +12206,7 @@
         <v>10</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C100" s="10">
         <v>347</v>
@@ -12195,7 +12277,7 @@
         <v>10</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C101" s="10">
         <v>347</v>
@@ -12277,10 +12359,10 @@
     </row>
     <row r="103" spans="1:27" ht="38.450000000000003">
       <c r="A103" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="5">
@@ -12346,10 +12428,10 @@
     </row>
     <row r="104" spans="1:27" ht="19.149999999999999">
       <c r="A104" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="5">
@@ -12415,10 +12497,10 @@
     </row>
     <row r="105" spans="1:27" ht="19.149999999999999">
       <c r="A105" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="5">
@@ -12484,10 +12566,10 @@
     </row>
     <row r="106" spans="1:27" ht="19.149999999999999">
       <c r="A106" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="5">
@@ -12553,10 +12635,10 @@
     </row>
     <row r="107" spans="1:27" ht="38.450000000000003">
       <c r="A107" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="5">
@@ -12622,10 +12704,10 @@
     </row>
     <row r="108" spans="1:27" ht="19.149999999999999">
       <c r="A108" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="5">
@@ -12691,10 +12773,10 @@
     </row>
     <row r="109" spans="1:27" ht="38.450000000000003">
       <c r="A109" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="5">
@@ -12760,10 +12842,10 @@
     </row>
     <row r="110" spans="1:27" ht="38.450000000000003">
       <c r="A110" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="5">
@@ -13825,186 +13907,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -14024,8 +13926,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S3:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 G3 M3 Y3" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -14043,7 +13945,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14073,38 +13975,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="D1" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -14117,76 +14019,76 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N2" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y2" s="41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z2" s="41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="38.25">
@@ -14265,7 +14167,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>478</v>
@@ -14336,7 +14238,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>478</v>
@@ -14407,7 +14309,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1">
         <v>478</v>
@@ -14478,7 +14380,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1">
         <v>478</v>
@@ -14549,7 +14451,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1">
         <v>478</v>
@@ -14620,7 +14522,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1">
         <v>478</v>
@@ -14691,7 +14593,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1">
         <v>478</v>
@@ -14834,7 +14736,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1">
         <v>516</v>
@@ -14905,7 +14807,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1">
         <v>516</v>
@@ -14976,7 +14878,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1">
         <v>516</v>
@@ -15047,7 +14949,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>516</v>
@@ -15118,7 +15020,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1">
         <v>516</v>
@@ -15189,7 +15091,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1">
         <v>516</v>
@@ -15260,7 +15162,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" s="1">
         <v>516</v>
@@ -15403,7 +15305,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1">
         <v>547</v>
@@ -15474,7 +15376,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1">
         <v>547</v>
@@ -15545,7 +15447,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1">
         <v>547</v>
@@ -15616,7 +15518,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25" s="1">
         <v>547</v>
@@ -15687,7 +15589,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1">
         <v>547</v>
@@ -15758,7 +15660,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1">
         <v>547</v>
@@ -15829,7 +15731,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1">
         <v>547</v>
@@ -15900,7 +15802,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C29" s="1">
         <v>547</v>
@@ -15972,7 +15874,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1">
         <v>489</v>
@@ -16043,7 +15945,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1">
         <v>489</v>
@@ -16114,7 +16016,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1">
         <v>489</v>
@@ -16185,7 +16087,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1">
         <v>489</v>
@@ -16256,7 +16158,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C35" s="1">
         <v>489</v>
@@ -16327,7 +16229,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1">
         <v>489</v>
@@ -16398,7 +16300,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="1">
         <v>489</v>
@@ -16469,7 +16371,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1">
         <v>489</v>
@@ -16540,7 +16442,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C39" s="1">
         <v>489</v>
@@ -16611,7 +16513,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="1">
         <v>489</v>
@@ -16682,7 +16584,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1">
         <v>489</v>
@@ -16754,7 +16656,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1">
         <v>449</v>
@@ -16825,7 +16727,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1">
         <v>449</v>
@@ -16896,7 +16798,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1">
         <v>449</v>
@@ -16967,7 +16869,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1">
         <v>449</v>
@@ -17038,7 +16940,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1">
         <v>449</v>
@@ -17109,7 +17011,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1">
         <v>449</v>
@@ -17180,7 +17082,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" s="1">
         <v>449</v>
@@ -17251,7 +17153,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C50" s="1">
         <v>449</v>
@@ -17322,7 +17224,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1">
         <v>449</v>
@@ -17393,7 +17295,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C52" s="1">
         <v>449</v>
@@ -17464,7 +17366,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C53" s="1">
         <v>449</v>
@@ -17536,7 +17438,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1">
         <v>462</v>
@@ -17611,7 +17513,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1">
         <v>462</v>
@@ -17686,7 +17588,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C57" s="1">
         <v>462</v>
@@ -17761,7 +17663,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C58" s="1">
         <v>462</v>
@@ -17836,7 +17738,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1">
         <v>462</v>
@@ -17911,7 +17813,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1">
         <v>462</v>
@@ -17986,7 +17888,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C61" s="1">
         <v>462</v>
@@ -18061,7 +17963,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C62" s="1">
         <v>462</v>
@@ -18136,7 +18038,7 @@
         <v>6</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C63" s="1">
         <v>462</v>
@@ -18207,7 +18109,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C64" s="1">
         <v>462</v>
@@ -18282,7 +18184,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C65" s="1">
         <v>462</v>
@@ -18358,7 +18260,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C67" s="10">
         <v>500</v>
@@ -18429,7 +18331,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C68" s="10">
         <v>500</v>
@@ -18500,7 +18402,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C69" s="10">
         <v>500</v>
@@ -18571,7 +18473,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C70" s="10">
         <v>500</v>
@@ -18642,7 +18544,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C71" s="10">
         <v>500</v>
@@ -18713,7 +18615,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10">
         <v>500</v>
@@ -18784,7 +18686,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C73" s="10">
         <v>500</v>
@@ -18855,7 +18757,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C74" s="10">
         <v>500</v>
@@ -18926,7 +18828,7 @@
         <v>7</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C75" s="10">
         <v>500</v>
@@ -18997,7 +18899,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C76" s="10">
         <v>500</v>
@@ -19068,7 +18970,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C77" s="10">
         <v>500</v>
@@ -19140,7 +19042,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10">
         <v>447</v>
@@ -19211,7 +19113,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C80" s="10">
         <v>447</v>
@@ -19282,7 +19184,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C81" s="10">
         <v>447</v>
@@ -19353,7 +19255,7 @@
         <v>8</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C82" s="10">
         <v>447</v>
@@ -19424,7 +19326,7 @@
         <v>8</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C83" s="10">
         <v>447</v>
@@ -19495,7 +19397,7 @@
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C84" s="10">
         <v>447</v>
@@ -19566,7 +19468,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C85" s="10">
         <v>447</v>
@@ -19637,7 +19539,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C86" s="10">
         <v>447</v>
@@ -19708,7 +19610,7 @@
         <v>8</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C87" s="10">
         <v>447</v>
@@ -19779,7 +19681,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C88" s="10">
         <v>447</v>
@@ -19850,7 +19752,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C89" s="10">
         <v>447</v>
@@ -19922,7 +19824,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C91" s="10">
         <v>437</v>
@@ -19997,7 +19899,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10">
         <v>437</v>
@@ -20072,7 +19974,7 @@
         <v>9</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C93" s="10">
         <v>437</v>
@@ -20143,7 +20045,7 @@
         <v>9</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C94" s="10">
         <v>437</v>
@@ -20218,7 +20120,7 @@
         <v>9</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C95" s="10">
         <v>437</v>
@@ -20289,7 +20191,7 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10">
         <v>437</v>
@@ -20364,7 +20266,7 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C97" s="10">
         <v>437</v>
@@ -20439,7 +20341,7 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C98" s="10">
         <v>437</v>
@@ -20514,7 +20416,7 @@
         <v>9</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C99" s="10">
         <v>437</v>
@@ -20585,7 +20487,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C100" s="10">
         <v>437</v>
@@ -20660,7 +20562,7 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C101" s="10">
         <v>437</v>
@@ -20736,7 +20638,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C103" s="10">
         <v>347</v>
@@ -20811,7 +20713,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C104" s="10">
         <v>347</v>
@@ -20886,7 +20788,7 @@
         <v>10</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C105" s="10">
         <v>347</v>
@@ -20961,7 +20863,7 @@
         <v>10</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C106" s="10">
         <v>347</v>
@@ -21036,7 +20938,7 @@
         <v>10</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C107" s="10">
         <v>347</v>
@@ -21111,7 +21013,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C108" s="10">
         <v>347</v>
@@ -21186,7 +21088,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C109" s="10">
         <v>347</v>
@@ -21261,7 +21163,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C110" s="10">
         <v>347</v>
@@ -21336,7 +21238,7 @@
         <v>10</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C111" s="10">
         <v>347</v>
@@ -21409,7 +21311,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C112" s="10">
         <v>347</v>
@@ -21484,7 +21386,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C113" s="10">
         <v>347</v>
@@ -21557,10 +21459,10 @@
     <row r="114" spans="1:28" s="7" customFormat="1"/>
     <row r="115" spans="1:28" ht="38.450000000000003">
       <c r="A115" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="5">
@@ -21626,10 +21528,10 @@
     </row>
     <row r="116" spans="1:28" ht="19.149999999999999">
       <c r="A116" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="5">
@@ -21695,10 +21597,10 @@
     </row>
     <row r="117" spans="1:28" ht="19.149999999999999">
       <c r="A117" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="5">
@@ -21764,10 +21666,10 @@
     </row>
     <row r="118" spans="1:28" ht="19.149999999999999">
       <c r="A118" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="5">
@@ -21833,10 +21735,10 @@
     </row>
     <row r="119" spans="1:28" ht="38.450000000000003">
       <c r="A119" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="5">
@@ -21902,10 +21804,10 @@
     </row>
     <row r="120" spans="1:28" ht="19.149999999999999">
       <c r="A120" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5">
@@ -21971,10 +21873,10 @@
     </row>
     <row r="121" spans="1:28" ht="38.450000000000003">
       <c r="A121" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="5">
@@ -22040,10 +21942,10 @@
     </row>
     <row r="122" spans="1:28" ht="38.450000000000003">
       <c r="A122" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="5">
@@ -22618,186 +22520,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C115:C122 C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C91:C101 C103:C113" name="Textbooks"/>
@@ -22815,8 +22537,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
